--- a/tools/excel/dgssi/exigences-de-qualification-des-prestataires-de-services-cloud.xlsx
+++ b/tools/excel/dgssi/exigences-de-qualification-des-prestataires-de-services-cloud.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\BGRASI\GRC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericlaubacher/Documents/GitHub/ciso-assistant-community/tools/excel/dgssi/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7565DADB-A089-844E-9465-0BBC004F1EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19275" windowHeight="6375" activeTab="2"/>
+    <workbookView xWindow="1220" yWindow="840" windowWidth="33060" windowHeight="19000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -18,12 +19,25 @@
     <sheet name="scores_meta" sheetId="4" r:id="rId4"/>
     <sheet name="scores_content" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="325">
   <si>
     <t>type</t>
   </si>
@@ -788,48 +802,6 @@
 </t>
   </si>
   <si>
-    <t>Les responsables des entités et infrastructures d’importance vitale doivent, lorsqu’ils ont recours à des services Cloud pour l’hébergement, la gestion ou l’exploitation de leurs systèmes ou données sensibles, faire appel à des prestataires qualifiés par l’autorité nationale de cybersécurité (Direction Générale de la Sécurité des Systèmes d’Information), selon les dispositions prévues par le décret n°2-24-921 du 18 rabii II 1446 (22 octobre 2024) relatif au recours aux prestataires de services Cloud par les entités et les infrastructures d’importance vitale disposant de systèmes d’information ou de données sensibles.
-Le présent référentiel, qui s’inspire des meilleures pratiques internationales, définit les exigences spécifiques auxquelles doit se conformer un prestataire de services cloud, désigné ci-après par « prestataire de services », pour être qualifié à fournir des services conformément aux dispositions du décret précité.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le processus de qualification se déroule en quatre (04) étapes conformément aux exigences des articles 6,7,8,9 et 10 du décret précité n°2-24-921.
-Le modèle de demande de qualification ainsi que les modèles d’engagement constituant le dossier de qualification sont publiés sur le site web de l’autorité nationale de cybersécurité. En ce qui concerne l’examen du dossier, l’autorité nationale de cybersécurité peut demander, en plus des documents requis au titre de l’article 6 du décret n°2-24-921, tous documents ou informations complémentaires utiles à l'instruction du dossier concernant le prestataire de services lui-même ou un ou plusieurs de ses sous-traitants. Elle peut aussi demander toute explication ou justification, notamment au sujet des statuts de la société, de l’identité des associés, des personnes impliquées dans la gestion et l’exploitation des services ou des attestations de référence. </t>
-  </si>
-  <si>
-    <t>Dans le cadre de la qualification, les exigences ci-après détaillées sont opposables aux prestataires de services uniquement sur le périmètre (systèmes et plateformes) qui est sous leur responsabilités. Le modèle de répartition des responsabilités entre prestataire de services et l’entité ou l’infrastructure d’importance vitale disposant de systèmes d’information ou de données sensibles désignées dans le présent référentiel par « commanditaire », est donné à titre indicatif.
-IaaS :
-Données : Responsabilité du commanditaire
-Applications : Responsabilité du commanditaire
-Runtimes : Responsabilité du commanditaire
-Middlewares : Responsabilité du commanditaire
-Systèmes d’Exploitation : Responsabilité du commanditaire
-Virtualisation :  Responsabilité du prestataire de services 
-Serveurs : Responsabilité du prestataire de services 
-Stockage : Responsabilité du prestataire de services 
-Réseaux : Responsabilité du prestataire de services 
-Paas :
-Données : Responsabilité du commanditaire
-Applications : Responsabilité du commanditaire
-Runtimes :  Responsabilité du prestataire de services 
-Middlewares :  Responsabilité du prestataire de services 
-Systèmes d’Exploitation :  Responsabilité du prestataire de services 
-Virtualisation :  Responsabilité du prestataire de services 
-Serveurs : Responsabilité du prestataire de services 
-Stockage : Responsabilité du prestataire de services 
-Réseaux : Responsabilité du prestataire de services 
-SaaS :
-Données : Responsabilité du commanditaire
-Applications :  Responsabilité du prestataire de services 
-Runtimes :  Responsabilité du prestataire de services 
-Middlewares :  Responsabilité du prestataire de services 
-Systèmes d’Exploitation :  Responsabilité du prestataire de services 
-Virtualisation :  Responsabilité du prestataire de services 
-Serveurs : Responsabilité du prestataire de services 
-Stockage : Responsabilité du prestataire de services 
-Réseaux : Responsabilité du prestataire de services 
-Sont assimilés à des services IaaS dans le cadre du présent référentiel les prestations de type hébergement externe classique qu’il soit dédié ou partagé. Les services de colocation ne sont pas régis par le présent référentiel.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ce chapitre a pour objet de garantir que le prestataire de services dispose de politiques et d'instructions en matière de sécurité qui couvrent les exigences de sécurité tout en soutenant les besoins métier liés à la fourniture du service. Ces politiques doivent être clairement définies, accessibles et suivies pour assurer la conformité et la gestion des risques de sécurité. </t>
   </si>
   <si>
@@ -1395,22 +1367,6 @@
     <t>urn:bassou:risk:framework:qualification_services_cloud_iiv</t>
   </si>
   <si>
-    <t>– En application des dispositions de l’article 4 du décret susvisé n° 2-24-921, est fixé
-dans l’annexe du présent arrêté le référentiel des exigences de qualification des prestataires de services Cloud.</t>
-  </si>
-  <si>
-    <t>ARTICLE PREMIER</t>
-  </si>
-  <si>
-    <t>Annexe</t>
-  </si>
-  <si>
-    <t>Contexte et objectifs</t>
-  </si>
-  <si>
-    <t>Processus de qualification</t>
-  </si>
-  <si>
     <t>Rôles et responsabilités</t>
   </si>
   <si>
@@ -1601,9 +1557,6 @@
   </si>
   <si>
     <t>Protection des données à caractère personnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exigences de qualification des Prestataires de services cloud </t>
   </si>
   <si>
     <t>Politiques de sécurité de l’information et gestion du risque</t>
@@ -1714,7 +1667,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1795,7 +1748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1810,7 +1763,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2118,14 +2070,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="113.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="113.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2133,15 +2085,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2149,7 +2101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2157,15 +2109,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2173,7 +2125,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2181,7 +2133,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2189,7 +2141,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2197,7 +2149,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -2211,15 +2163,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2227,31 +2179,31 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2259,7 +2211,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2267,7 +2219,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2275,7 +2227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -2283,7 +2235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -2297,16 +2249,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E105"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E100"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="78.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="91.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="78.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -2323,50 +2275,52 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>24</v>
-      </c>
+    <row r="2" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
       <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>290</v>
+      </c>
       <c r="D2" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="160" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="144" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
@@ -2374,16 +2328,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -2391,1648 +2345,1569 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>298</v>
+        <v>227</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B7" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>299</v>
+        <v>228</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="208" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="244" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="128" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="224" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="320" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="288" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="335" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4">
-        <v>4</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="375" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="4">
-        <v>4</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="4">
-        <v>4</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="4">
-        <v>4</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D29" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="160" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="350" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="4">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="4">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="4">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="256" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="4">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="192" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="4">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="320" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="4">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4">
-        <v>3</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="4">
-        <v>4</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="4">
-        <v>4</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D39" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="4">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="4">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="4">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="192" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="4">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="224" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="4">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="224" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="4">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="4">
-        <v>4</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="4">
-        <v>4</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="4">
-        <v>4</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4">
-        <v>3</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="259.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="4">
-        <v>4</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="4">
-        <v>4</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="4">
-        <v>4</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="D45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4">
+        <v>1</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="4">
-        <v>4</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4">
-        <v>4</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="4">
-        <v>4</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4">
-        <v>3</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="D46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="4">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="4">
-        <v>4</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="D47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="224" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="4">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="4">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" s="4">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="256" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="4">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="350" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="4">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="192" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="4">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="4">
-        <v>4</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="240" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="4">
-        <v>4</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="D53" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="4">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="4">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="4">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="4">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="4">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" s="4">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="4">
-        <v>4</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="D59" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="4">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4">
+        <v>1</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D61" s="5"/>
+      <c r="E61" s="7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="4">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="315" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="4">
-        <v>4</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="330" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="4">
-        <v>4</v>
-      </c>
-      <c r="C33" s="5" t="s">
+      <c r="D62" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63" s="4">
+        <v>2</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="4">
+        <v>2</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4">
+        <v>1</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="345" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="4">
-        <v>4</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="D65" s="4"/>
+      <c r="E65" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="160" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66" s="4">
+        <v>2</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="160" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" s="4">
+        <v>2</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B68" s="4">
+        <v>2</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" s="4">
+        <v>2</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="4">
+        <v>2</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="4">
+        <v>2</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4">
+        <v>1</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4">
-        <v>3</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="4">
-        <v>4</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" s="4">
-        <v>4</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="405" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="4">
-        <v>4</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" s="4">
-        <v>4</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="4">
-        <v>4</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="270" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B41" s="4">
-        <v>4</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="4">
-        <v>3</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="4">
-        <v>4</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="330" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B44" s="4">
-        <v>4</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="D72" s="4"/>
+      <c r="E72" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="128" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" s="4">
+        <v>2</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="4">
+        <v>2</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="4">
+        <v>2</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" s="4">
+        <v>2</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" s="4">
+        <v>2</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4">
+        <v>1</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" s="4"/>
+      <c r="E78" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="4">
+        <v>2</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="260" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" s="4">
+        <v>2</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" s="4">
-        <v>4</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B46" s="4">
-        <v>4</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B47" s="4">
-        <v>4</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="210" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B48" s="4">
-        <v>4</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="255" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B49" s="4">
-        <v>4</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="240" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B50" s="4">
-        <v>4</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="D80" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" s="4">
+        <v>2</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4">
-        <v>3</v>
-      </c>
-      <c r="C51" s="5" t="s">
+      <c r="D81" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" s="4">
+        <v>2</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B52" s="4">
-        <v>4</v>
-      </c>
-      <c r="C52" s="5" t="s">
+      <c r="D82" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B83" s="4">
+        <v>2</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="225" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B53" s="4">
-        <v>4</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B54" s="4">
-        <v>4</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B55" s="4">
-        <v>4</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="300" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B56" s="4">
-        <v>4</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="345" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B57" s="4">
-        <v>4</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="255" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B58" s="4">
-        <v>4</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="D83" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="4">
+        <v>2</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B59" s="4">
-        <v>4</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="4">
-        <v>4</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="4">
-        <v>4</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B62" s="4">
-        <v>4</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="210" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" s="4">
-        <v>4</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" s="4">
-        <v>4</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="D85" s="4"/>
+      <c r="E85" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86" s="4">
+        <v>2</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" s="4">
-        <v>4</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4">
-        <v>3</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B67" s="4">
-        <v>4</v>
-      </c>
-      <c r="C67" s="4" t="s">
+      <c r="D86" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87" s="4">
+        <v>2</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B68" s="4">
-        <v>4</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B69" s="4">
-        <v>4</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4">
-        <v>3</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="D87" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="4">
+        <v>2</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B71" s="4">
-        <v>4</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B72" s="4">
-        <v>4</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B73" s="4">
-        <v>4</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B74" s="4">
-        <v>4</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B75" s="4">
-        <v>4</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B76" s="4">
-        <v>4</v>
-      </c>
-      <c r="C76" s="4" t="s">
+      <c r="D88" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B89" s="4">
+        <v>2</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90" s="4">
+        <v>2</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B91" s="4">
+        <v>2</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4">
+        <v>1</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D76" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4">
-        <v>3</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="8" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B78" s="4">
-        <v>4</v>
-      </c>
-      <c r="C78" s="4" t="s">
+      <c r="D92" s="4"/>
+      <c r="E92" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B93" s="4">
+        <v>2</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="D78" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B79" s="4">
-        <v>4</v>
-      </c>
-      <c r="C79" s="4" t="s">
+      <c r="D93" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B94" s="4">
+        <v>2</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" s="4">
+        <v>2</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D79" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="345" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B80" s="4">
-        <v>4</v>
-      </c>
-      <c r="C80" s="4" t="s">
+      <c r="D95" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" s="4">
+        <v>2</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D80" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B81" s="4">
-        <v>4</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="405" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B82" s="4">
-        <v>4</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4">
-        <v>3</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D83" s="4"/>
-      <c r="E83" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B84" s="4">
-        <v>4</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B85" s="4">
-        <v>4</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B86" s="4">
-        <v>4</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B87" s="4">
-        <v>4</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B88" s="4">
-        <v>4</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="360" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B89" s="4">
-        <v>4</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4">
-        <v>3</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D90" s="4"/>
-      <c r="E90" s="8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B91" s="4">
-        <v>4</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="330" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B92" s="4">
-        <v>4</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="285" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B93" s="4">
-        <v>4</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="390" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B94" s="4">
-        <v>4</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="255" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B95" s="4">
-        <v>4</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="210" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B96" s="4">
-        <v>4</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>330</v>
-      </c>
       <c r="D96" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="4">
-        <v>3</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>291</v>
+        <v>1</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="D97" s="4"/>
-      <c r="E97" s="8" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="E97" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B98" s="4">
-        <v>4</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>292</v>
+        <v>2</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="224" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B99" s="4">
-        <v>4</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="365" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B100" s="4">
-        <v>4</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>293</v>
+        <v>2</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>289</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B101" s="4">
-        <v>4</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4">
-        <v>3</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="D102" s="4"/>
-      <c r="E102" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E100" s="7" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B103" s="4">
-        <v>4</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B104" s="4">
-        <v>4</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="375" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B105" s="4">
-        <v>4</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>225</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C16:D41 C105 C44:D104">
+  <conditionalFormatting sqref="C11:D36 C100 C39:D99">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -4046,7 +3921,21 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C43:D43">
+  <conditionalFormatting sqref="C37:D37">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0EEB8208-A0BF-47DE-A46A-8743812E1F55}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C38:D38">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -4056,20 +3945,6 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{00BFA3DA-3FA3-4F09-98FE-486944C54EE7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C42:D42">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0EEB8208-A0BF-47DE-A46A-8743812E1F55}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4087,7 +3962,18 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C16:D41 C105 C44:D104</xm:sqref>
+          <xm:sqref>C11:D36 C100 C39:D99</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0EEB8208-A0BF-47DE-A46A-8743812E1F55}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C37:D37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{00BFA3DA-3FA3-4F09-98FE-486944C54EE7}">
@@ -4098,18 +3984,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C43:D43</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0EEB8208-A0BF-47DE-A46A-8743812E1F55}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>C42:D42</xm:sqref>
+          <xm:sqref>C38:D38</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4118,11 +3993,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4130,7 +4005,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4144,11 +4019,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -4159,7 +4034,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4167,7 +4042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4176,7 +4051,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4185,7 +4060,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4194,7 +4069,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4203,7 +4078,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
